--- a/Academic_CV_Structure_Template.xlsx
+++ b/Academic_CV_Structure_Template.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IIT BBSR\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my-CV\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" firstSheet="8" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Personal_Info" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="277">
   <si>
     <t>Field</t>
   </si>
@@ -243,13 +243,1463 @@
   </si>
   <si>
     <t>Client</t>
+  </si>
+  <si>
+    <t>Mondal, G., and Jain, S.K.</t>
+  </si>
+  <si>
+    <t>Design of Non-structural Elements for Buildings: A review of Codal Provisions</t>
+  </si>
+  <si>
+    <t>Indian Concrete Journal</t>
+  </si>
+  <si>
+    <t>Proposed Draft for IS1893 on Design of Non-structural Elements</t>
+  </si>
+  <si>
+    <t>Mondal, G., and Rai, D.C.</t>
+  </si>
+  <si>
+    <t>Need for Earthquake-Resistant Design of Harbour Structures in India in view of Their Performance during the 2004 Sumatra Earthquake</t>
+  </si>
+  <si>
+    <t>Current Science</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tang, A.,  Rai, D.C, Ames, D., Murty, C.V.R., Jain, S.K., Dash, S.R., Kaushik, H.B., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, Murugesh, G., Plant G., McLaughlin, J., Yashinsky, M., Eskijian, M., and Surrampalli, R.</t>
+    </r>
+  </si>
+  <si>
+    <t>Lifeline Systems in the Andaman and Nicobar Islands (India) after the December 2004 Great Sumatra Earthquake and Indian Ocean Tsunami</t>
+  </si>
+  <si>
+    <t>Earthquake Spectra</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Rai, D.C, Murty, C.V.R., Jain, S.K., Kaushik, H.B., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, Dash, S.R., Tang, A., Yashinsky, M., and Eskijian, M.</t>
+    </r>
+  </si>
+  <si>
+    <t>The Effect of the December 2004 Great Sumatra Earthquake and Indian Ocean Tsunami on Transportation Systems in India’s Andaman and Nicobar Islands</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Murty, C.V.R, Rai, D.C., Jain, S.K., Kaushik, H.B., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, and Dash, S.R.</t>
+    </r>
+  </si>
+  <si>
+    <t>Performance of Structures in the Andaman and Nicobar Islands (India) during the December 2004 Great Sumatra Earthquake and Indian Ocean Tsunami</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Jain, S.K., Ingle, R.K., and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Proposed Codal Provisions for Design and Detailing of Beam-Column Joints in Seismic Regions</t>
+  </si>
+  <si>
+    <t>Lateral Stiffness of Masonry Infilled RC Frames with Central Opening</t>
+  </si>
+  <si>
+    <t>Performance of Harbour Structures in Andaman Islands during 2004 Sumatra Earthquake</t>
+  </si>
+  <si>
+    <t>Engineering Structure</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Rai, D.C, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, Singhal, V., Parool, N., Pradhan, T., and Mitra, K. </t>
+    </r>
+  </si>
+  <si>
+    <t>M6.9 Nepal-Sikkim Border Earthquake of September 18, 2011</t>
+  </si>
+  <si>
+    <t>Mondal, G., Prashant, A., and Jain, S.K.</t>
+  </si>
+  <si>
+    <t>Significance of Interface Nonlinearity on Seismic Response of Well-Pier System in Cohesionless Soil</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Rai, D.C, Singhal, V., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, Parool, N., Pradhan, T., and Mitra, K.</t>
+    </r>
+  </si>
+  <si>
+    <t>Reconnaissance Report of the M6.9 Sikkim (India-Nepal Border) Earthquake of September 18, 2011</t>
+  </si>
+  <si>
+    <t>Geomatics, Natural Hazards and Risk</t>
+  </si>
+  <si>
+    <t>Simplified Seismic Analysis of Soil-Well-Pier System for Bridges</t>
+  </si>
+  <si>
+    <t>Soil Dynamics and Earthquake Engineering</t>
+  </si>
+  <si>
+    <t>Mondal, G., and Tesfamariam, S.</t>
+  </si>
+  <si>
+    <t>Effect of Vertical Irregularity and Thickness of Unreinforced Masonry Infill on the Robustness of RC Frame Buildings</t>
+  </si>
+  <si>
+    <t>Earthquake Engineering and Structural Dynamics</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tesfamariam, S., Goda, K., and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mondal, G. </t>
+    </r>
+  </si>
+  <si>
+    <t>Seismic Vulnerability of RC Frame with Unreinforced Masonry Infill Due to Mainshock-Aftershock Earthquake Sequences</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Chavan, D.S., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> and Prashant, A.</t>
+    </r>
+  </si>
+  <si>
+    <t>Seismic Analysis of Nailed Soil Slope Considering Interface Effects</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nair, G.S., Dash, S.R., and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+  </si>
+  <si>
+    <t>Review of Pipeline Performance during Earthquakes since 1906</t>
+  </si>
+  <si>
+    <t>Journal of Performance of Constructed Facilities, ASCE,</t>
+  </si>
+  <si>
+    <t>Varma, T. V., Sarkar S., and Mondal, G.</t>
+  </si>
+  <si>
+    <t>Buckling Restrained Sizing and Shape Optimization of Truss Structures</t>
+  </si>
+  <si>
+    <t>Journal of Structural Engineering, ASCE</t>
+  </si>
+  <si>
+    <r>
+      <t>Nair</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">G.S., Dash, S.R., and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Statistical Analysis for the Seismic Risk Assessment of Pipelines in India</t>
+  </si>
+  <si>
+    <t>Journal of Pipeline Systems - Engineering and Practice, ASCE</t>
+  </si>
+  <si>
+    <t>Numerical Study of Horizontally Bent Buried Steel Pipelines Subjected to Oblique Faulting</t>
+  </si>
+  <si>
+    <t>ASME Journal of Pressure Vessel Technology</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kumawat, S.R. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mondal, G. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>and Dash, S.R.,</t>
+    </r>
+  </si>
+  <si>
+    <t>Experimental assessment of post-earthquake retrofitted reinforced concrete frame partially infilled with fly-ash brick</t>
+  </si>
+  <si>
+    <t>Earthquakes and Structures</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Taori, P.,Dash, S.R., and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+  </si>
+  <si>
+    <t>Seismic Response of Post Tensioned Hybrid Shear Walls with External Energy Dissipating Reinforcement (EEDR)</t>
+  </si>
+  <si>
+    <t>Journal of Earthquake Engineering</t>
+  </si>
+  <si>
+    <t>Tiwari, S., Mondal, G. , Dash, S.R, and Roy, K.</t>
+  </si>
+  <si>
+    <t>Experimental investigation of unbonded Reinforced Concrete PT shear wall under lateral loading: A state-of-the-art review</t>
+  </si>
+  <si>
+    <t>Journal of Building Engineering</t>
+  </si>
+  <si>
+    <t>Pandit, U.K. Mondal, G. and Punera, D.</t>
+  </si>
+  <si>
+    <t>Lateral torsional buckling analysis of corrugated steel web girders using homogenization approach</t>
+  </si>
+  <si>
+    <t>Journal of Construction Steel Research</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Jaiswal, D. K. , </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, Dash, S.R., and Mishra, M.</t>
+    </r>
+  </si>
+  <si>
+    <t>Damage detection technique in existing structures using vibration-based model updating</t>
+  </si>
+  <si>
+    <t>Structural Monitoring and Maintenance</t>
+  </si>
+  <si>
+    <t>Tiwari, S., Dash, S.R., Mondal, G., and Roy, K.</t>
+  </si>
+  <si>
+    <t>Analysis and Design of RC Unbonded PT Shear Wall in Isolation and Integrated in Building: A State-of-the-art Review</t>
+  </si>
+  <si>
+    <t>Structures</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Singha, B., and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+  </si>
+  <si>
+    <t>Effect of Partially Infill Walls on the Lateral Response of ReinforcedConcrete Frames</t>
+  </si>
+  <si>
+    <t>Response of Horizontally Bent Buried Pipelines Subjected to Strike-slip Faulting: A Numerical Investigation</t>
+  </si>
+  <si>
+    <t>Lateral stiffness of partially infilled reinforced concrete (RC) frames</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pandit, U.K. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> and Punera, D.</t>
+    </r>
+  </si>
+  <si>
+    <t>Investigating the static, free vibration, and buckling responses of corrugated steel plate-made structures using efficient homogenization-based FE modelling</t>
+  </si>
+  <si>
+    <t>Recent Review and Comparative Assessment of Local Instability in Thin-Walled Corrugated Steel Web Girders</t>
+  </si>
+  <si>
+    <t>International Journal of Structural Stability and Dynamics</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Priyadarshini, M., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, and Dash, S.R,</t>
+    </r>
+  </si>
+  <si>
+    <t>Development of a non-conventional first-class fly ash brick and evaluation of its mechanical and durability properties</t>
+  </si>
+  <si>
+    <t>Journal of Materials in Civil Engineering</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Singha, B.N., Mohanta, A., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF434343"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF434343"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> and Dash, S.R.</t>
+    </r>
+  </si>
+  <si>
+    <t>Lateral Response of Special Ductile RC Frames Partially Infilled with Different Types of Brick Masonry: An Experimental Investigation</t>
+  </si>
+  <si>
+    <t>Bulletin of Earthquake Engineering</t>
+  </si>
+  <si>
+    <t>Seismic Performance of Partially Infilled RC Frames: A Finite Element-Based Simplified Modeling Approach </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priyadarshini, M., Mondal, G. , and Dash, S.R, </t>
+  </si>
+  <si>
+    <t>Influence of alkali activation and curing conditions on non-conventional fly ash bricks</t>
+  </si>
+  <si>
+    <t>Environmental Science and Pollution Research </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pandit, U.K. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and Punera, D.</t>
+    </r>
+  </si>
+  <si>
+    <t>Reliability-based shear design and safety assessment of corrugated steel web girders</t>
+  </si>
+  <si>
+    <t>Probabilistic Engineering Mechanics</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>174-182</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.engstruct.2007.03.015</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>1437-1446</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>1117–1145</t>
+  </si>
+  <si>
+    <t>DOI: 10.1193/1.4000074</t>
+  </si>
+  <si>
+    <t>99-111</t>
+  </si>
+  <si>
+    <t>DOI: 10.1080/19475705.2011.647336</t>
+  </si>
+  <si>
+    <t>42-55</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.soildyn.2011.08.002</t>
+  </si>
+  <si>
+    <t>205-223</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/eqe.2338</t>
+  </si>
+  <si>
+    <t>1427-1449</t>
+  </si>
+  <si>
+    <t>DOI: 10.1193/042313EQS111M.</t>
+  </si>
+  <si>
+    <t>480–491</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.soildyn.2017.06.024</t>
+  </si>
+  <si>
+    <t>04018083(1-18)</t>
+  </si>
+  <si>
+    <t>DOI: 10.1061/(ASCE)CF.1943-5509.0001214</t>
+  </si>
+  <si>
+    <t>04020048(1-12)</t>
+  </si>
+  <si>
+    <t>DOI: 10.1061/(ASCE)ST.1943-541X.0002590</t>
+  </si>
+  <si>
+    <t>04021053 (1-30)</t>
+  </si>
+  <si>
+    <t>DOI: 10.1061/(ASCE)PS.1949-1204.0000590</t>
+  </si>
+  <si>
+    <t>DOI: 10.1115/1.4054686</t>
+  </si>
+  <si>
+    <t>121-135</t>
+  </si>
+  <si>
+    <t>DOI: 10.12989/eas.2022.22.2.121</t>
+  </si>
+  <si>
+    <t>2911-2926</t>
+  </si>
+  <si>
+    <t>DOI: 10.1080/13632469.2020.1778587</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.jobe.2023.107504</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.jcsr.2023.108099</t>
+  </si>
+  <si>
+    <t>63-86</t>
+  </si>
+  <si>
+    <t>DOI: 10.12989/smm.2023.10.1.063</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.istruc.2023.06.121</t>
+  </si>
+  <si>
+    <t>4323–4362</t>
+  </si>
+  <si>
+    <t>DOI: 10.1080/13632469.2024.2376625</t>
+  </si>
+  <si>
+    <t>DOI: 10.1061/JPSEA2.PSENG-1480</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.istruc.2024.107532</t>
+  </si>
+  <si>
+    <t>DOI: 10.1016/j.istruc.2024.107643</t>
+  </si>
+  <si>
+    <t>DOI: 10.1142/S0219455425300022</t>
+  </si>
+  <si>
+    <t>DOI: 10.1061/JMCEE7.MTENG-19481</t>
+  </si>
+  <si>
+    <t>DOI: 10.1007/s10518-026-02439-3</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1002/esp4.70000</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s11356-026-37674-3</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.probengmech.2026.103935</t>
+  </si>
+  <si>
+    <t>Pandit, U.K., Jibhakate, D., Mondal, G. and Punera, D.</t>
+  </si>
+  <si>
+    <t>Influence of corrugation orientation on the elastic buckling capacity of corrugated steel plate shear walls</t>
+  </si>
+  <si>
+    <t>1st International Conference on Advanced Technology in Material Science and Engineering, ICATMSE-24</t>
+  </si>
+  <si>
+    <t>Singha, B and Mondal, G.M.</t>
+  </si>
+  <si>
+    <t>A Comparison of Ductile and Non-Ductile Detailing in Partially Infilled Reinforced Concrete Frame</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Jibhakate, D., Pandit, U.K., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> and Punera, D.</t>
+    </r>
+  </si>
+  <si>
+    <t>Effect of varying corrugation parameters of corrugated infill with RC frame using pushover analysis</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pandit, U.K. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> and Punera, D.</t>
+    </r>
+  </si>
+  <si>
+    <t>Homogenization-based numerical analysis of corrugated steel infill walls under lateral loading</t>
+  </si>
+  <si>
+    <r>
+      <t>18th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> World Conference on Earthquake Engineering, 18WCEE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Priyadarshini1, M., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> and Dash, S. R.</t>
+    </r>
+  </si>
+  <si>
+    <t>Influence of different types brick masonry in the performance of a RC framed building</t>
+  </si>
+  <si>
+    <r>
+      <t>18th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> World Conference on Earthquake Engineering</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Singha, B and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.M.</t>
+    </r>
+  </si>
+  <si>
+    <t>Investigating the impact of interface joint strength on the lateral response of partially infilled frames</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Syed, F.A.Q., Tiwari, S., Dash, S.R. and</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Mondal, G.</t>
+    </r>
+  </si>
+  <si>
+    <t>Optimisation study of passive energy dissipator configuration suitable for hybrid PT shear wall</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Tiwari, S., Dash, S.R. and</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Mondal, G.</t>
+    </r>
+  </si>
+  <si>
+    <t>Developments in the design of experiments for testing of hybrid post-tensioned shear wall</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vadlapudi, R.C.L.S.V., Singha, B, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>. and Dash, S.R.</t>
+    </r>
+  </si>
+  <si>
+    <t>Effect of toothed wall-frame connection on the lateral response of confined masonry</t>
+  </si>
+  <si>
+    <r>
+      <t>18th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> World Conference on Earthquake Engineering, 18WCEE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Anand, S., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> and Saravanan, T.J.</t>
+    </r>
+  </si>
+  <si>
+    <t>Hydrodynamic effects on the seismic fragility of two-span simply-supported deep sea water bridges</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Harshavardan, V., Reddy, S., Dash, S.R. and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+  </si>
+  <si>
+    <t>Experimental validation of RC beam-column joint designed and detailed as per Indian code</t>
+  </si>
+  <si>
+    <t>Homogenization-based efficient 1D finite element modelling of a corrugated steel web I-girder</t>
+  </si>
+  <si>
+    <t>13th Structural Engineering Convention, SEC-2023</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Jaiswal, D., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, and Dash, S.R.</t>
+    </r>
+  </si>
+  <si>
+    <t>Development of an Effective and Efficient Baseline Free Damage Detection Scheme for Structural Health Monitoring</t>
+  </si>
+  <si>
+    <t>Indian Structural Steel Conference</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ahamed, S.S., Saravanan, T.J. , </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, Rajasekharan, S.</t>
+    </r>
+  </si>
+  <si>
+    <t>Spectral finite element model for a curved beam with an edge crack using classical Love’s shell-type theory</t>
+  </si>
+  <si>
+    <t>The 8th World Conference on Structural Control and Monitoring (8WCSCM)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ahamed, S.S., Saravanan, T.J., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, Rajasekharan, S.</t>
+    </r>
+  </si>
+  <si>
+    <t>Analysis of curved beams with an edge crack using a higher-order spectral element model</t>
+  </si>
+  <si>
+    <t>1st International Conference on Mechanics of Solids</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Saravanan, T.J. , </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, Rajasekharan, S.</t>
+    </r>
+  </si>
+  <si>
+    <t>Simplified breathing crack element for spectral Timoshenko beam model</t>
+  </si>
+  <si>
+    <t>Srusti, B.H.T., Prashant, A., Mondal, G.</t>
+  </si>
+  <si>
+    <t>Modelling for Simplified Seismic Analysis of Soil-Pile System</t>
+  </si>
+  <si>
+    <t>Proceedings of the 1st Eurasian Conference on OpenSees: OpenSees Days Eurasia</t>
+  </si>
+  <si>
+    <t>Agarwal, M.P., Radhika, B., Mondal, G.</t>
+  </si>
+  <si>
+    <t>Estimation of Fragility Curves Using IDA Analysis</t>
+  </si>
+  <si>
+    <t>International Conference on Composite Materials and Structures, ICCMS 2017</t>
+  </si>
+  <si>
+    <t>Singh, P., Mondal, G.</t>
+  </si>
+  <si>
+    <t>Response of R.C. Frames with Partial Infill Subjected to Lateral In-Plane Loading</t>
+  </si>
+  <si>
+    <r>
+      <t>16th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> World Conference on Earthquake Engineering, 16WCEE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mondal, G. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Tesfamariam, S.</t>
+    </r>
+  </si>
+  <si>
+    <t>Assessment of Robustness of Masonry Infilled RC Frame Buildings with Consideration of Irregularities</t>
+  </si>
+  <si>
+    <r>
+      <t>15th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> World Conference on Earthquake Engineering, 15WCEE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Chavan, D.S.,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Mondal, G. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Prashant, A.</t>
+    </r>
+  </si>
+  <si>
+    <t>Permanent Displacement of Nailed Soil Slopes Subjected to Earthquake Loading</t>
+  </si>
+  <si>
+    <r>
+      <t>Rai, D.C.,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Mondal, G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>., Singhal, V., Parool, N. and Pradhan, T.</t>
+    </r>
+  </si>
+  <si>
+    <t>2011 Sikkim Earthquake: Effects on Building Stocks and Perspective on Growing Seismic Risk</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pradhan, T., Singhal, V., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mondal, G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>., Parool, N. and Rai, D.C.</t>
+    </r>
+  </si>
+  <si>
+    <t>Seismic Vulnerability of Buddhist Monasteries: Evidences from the 2011 Sikkim Earthquake and Dynamic Analyses</t>
+  </si>
+  <si>
+    <r>
+      <t>Mondal, G.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> and Jain, S.K.</t>
+    </r>
+  </si>
+  <si>
+    <t>Two-Dimensional Nonlinear Seismic Analysis of Soil-Well-Pier System Considering Soil Nonlinearity</t>
+  </si>
+  <si>
+    <t>9th U.S. National and 10th Canadian Conference on Earthquake Engineering</t>
+  </si>
+  <si>
+    <t>Effect of Nonlinearity in Pier and Well Foundation on Seismic Response of Bridges</t>
+  </si>
+  <si>
+    <r>
+      <t>14th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> World Conference on Earthquake Engineering, 14WCEE</t>
+    </r>
+  </si>
+  <si>
+    <t>Lateral Stiffness of Unreinforced Brick Infilled RC Frames with Central Openings</t>
+  </si>
+  <si>
+    <r>
+      <t>8th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> National Conference on Earthquake Engineering, 8NCEE</t>
+    </r>
+  </si>
+  <si>
+    <t>Bhubaneswar. India</t>
+  </si>
+  <si>
+    <t>Milan, Italy</t>
+  </si>
+  <si>
+    <t>Nagpur, India</t>
+  </si>
+  <si>
+    <t>Hyderabad, India</t>
+  </si>
+  <si>
+    <t>Orlando. Florida, USA</t>
+  </si>
+  <si>
+    <t>Porto, Portugal</t>
+  </si>
+  <si>
+    <t>Hong Kong, China</t>
+  </si>
+  <si>
+    <t>Santiago, Chile</t>
+  </si>
+  <si>
+    <t>Lisbon, Portugal</t>
+  </si>
+  <si>
+    <t>Toronto, Canada</t>
+  </si>
+  <si>
+    <t>Bejing, China</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,16 +1712,187 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF2E2E2E"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF434343"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF434343"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF0000FF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -279,15 +1900,193 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -956,7 +2755,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1002,14 +2801,1016 @@
         <v>40</v>
       </c>
     </row>
+    <row r="2" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2005</v>
+      </c>
+      <c r="E2" s="3">
+        <v>79</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J2" s="3">
+        <v>4.4710000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2005</v>
+      </c>
+      <c r="E3" s="5">
+        <v>79</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1.169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="252" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="8">
+        <v>2006</v>
+      </c>
+      <c r="E4" s="3">
+        <v>91</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J4" s="3">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="315" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2006</v>
+      </c>
+      <c r="E5" s="5">
+        <v>22</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3.528</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="315" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2006</v>
+      </c>
+      <c r="E6" s="3">
+        <v>22</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J6" s="3">
+        <v>3.718</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="299.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2006</v>
+      </c>
+      <c r="E7" s="5">
+        <v>22</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="J7" s="32">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="173.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2006</v>
+      </c>
+      <c r="E8" s="3">
+        <v>80</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J8" s="34">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2008</v>
+      </c>
+      <c r="E9" s="5">
+        <v>24</v>
+      </c>
+      <c r="F9" s="7">
+        <v>3</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="J9" s="5">
+        <v>3.718</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="189" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2008</v>
+      </c>
+      <c r="E10" s="3">
+        <v>30</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J10" s="34">
+        <v>2.3719999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2012</v>
+      </c>
+      <c r="E11" s="5">
+        <v>102</v>
+      </c>
+      <c r="F11" s="5">
+        <v>10</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="H11" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="J11" s="5">
+        <v>3.3119999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="189" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2012</v>
+      </c>
+      <c r="E12" s="3">
+        <v>28</v>
+      </c>
+      <c r="F12" s="3">
+        <v>3</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H12" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1.952</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="204.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2012</v>
+      </c>
+      <c r="E13" s="5">
+        <v>3</v>
+      </c>
+      <c r="F13" s="5">
+        <v>2</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="J13" s="5">
+        <v>1.0509999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="126" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2012</v>
+      </c>
+      <c r="E14" s="3">
+        <v>32</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J14" s="34">
+        <v>2.0179999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" s="7">
+        <v>2014</v>
+      </c>
+      <c r="E15" s="7">
+        <v>43</v>
+      </c>
+      <c r="F15" s="7">
+        <v>2</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="H15" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="J15" s="32">
+        <v>3.9940000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2015</v>
+      </c>
+      <c r="E16" s="2">
+        <v>31</v>
+      </c>
+      <c r="F16" s="2">
+        <v>3</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J16" s="34">
+        <v>5.3179999999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" s="7">
+        <v>2017</v>
+      </c>
+      <c r="E17" s="12">
+        <v>100</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="35" t="s">
+        <v>186</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="J17" s="32">
+        <v>3.6459999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E18" s="2">
+        <v>32</v>
+      </c>
+      <c r="F18" s="2">
+        <v>6</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="J18" s="34">
+        <v>1.825</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="20">
+        <v>2020</v>
+      </c>
+      <c r="E19" s="20">
+        <v>146</v>
+      </c>
+      <c r="F19" s="7">
+        <v>5</v>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="J19" s="32">
+        <v>2.9830000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2021</v>
+      </c>
+      <c r="E20" s="2">
+        <v>12</v>
+      </c>
+      <c r="F20" s="2">
+        <v>4</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J20" s="34"/>
+    </row>
+    <row r="21" spans="1:10" ht="173.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="7">
+        <v>2022</v>
+      </c>
+      <c r="E21" s="7">
+        <v>144</v>
+      </c>
+      <c r="F21" s="7">
+        <v>5</v>
+      </c>
+      <c r="G21" s="7"/>
+      <c r="H21" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="J21" s="32">
+        <v>1.952</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="2">
+        <v>2022</v>
+      </c>
+      <c r="E22" s="2">
+        <v>22</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J22" s="34"/>
+    </row>
+    <row r="23" spans="1:10" ht="220.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" s="7">
+        <v>2022</v>
+      </c>
+      <c r="E23" s="7">
+        <v>26</v>
+      </c>
+      <c r="F23" s="7">
+        <v>6</v>
+      </c>
+      <c r="G23" s="7"/>
+      <c r="H23" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="J23" s="32"/>
+    </row>
+    <row r="24" spans="1:10" ht="236.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2023</v>
+      </c>
+      <c r="E24" s="2">
+        <v>78</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J24" s="34"/>
+    </row>
+    <row r="25" spans="1:10" ht="189" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="7">
+        <v>2023</v>
+      </c>
+      <c r="E25" s="7">
+        <v>210</v>
+      </c>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="I25" s="7"/>
+      <c r="J25" s="32"/>
+    </row>
+    <row r="26" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" s="14">
+        <v>2023</v>
+      </c>
+      <c r="E26" s="2">
+        <v>10</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="38" t="s">
+        <v>197</v>
+      </c>
+      <c r="I26" s="2"/>
+      <c r="J26" s="34"/>
+    </row>
+    <row r="27" spans="1:10" ht="252" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="7">
+        <v>2023</v>
+      </c>
+      <c r="E27" s="7">
+        <v>56</v>
+      </c>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="J27" s="32"/>
+    </row>
+    <row r="28" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2024</v>
+      </c>
+      <c r="E28" s="2">
+        <v>28</v>
+      </c>
+      <c r="F28" s="2">
+        <v>15</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="I28" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="J28" s="34"/>
+    </row>
+    <row r="29" spans="1:10" ht="220.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" s="7">
+        <v>2024</v>
+      </c>
+      <c r="E29" s="7">
+        <v>15</v>
+      </c>
+      <c r="F29" s="7">
+        <v>3</v>
+      </c>
+      <c r="G29" s="26"/>
+      <c r="H29" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="J29" s="41">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="126" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" s="2">
+        <v>2024</v>
+      </c>
+      <c r="E30" s="2">
+        <v>70</v>
+      </c>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="1:10" ht="299.25" x14ac:dyDescent="0.25">
+      <c r="A31" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="D31" s="7">
+        <v>2024</v>
+      </c>
+      <c r="E31" s="7">
+        <v>70</v>
+      </c>
+      <c r="F31" s="7"/>
+    </row>
+    <row r="32" spans="1:10" ht="236.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D32" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E32" s="2">
+        <v>25</v>
+      </c>
+      <c r="F32" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="220.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="D33" s="7">
+        <v>2025</v>
+      </c>
+      <c r="E33" s="7">
+        <v>37</v>
+      </c>
+      <c r="F33" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="283.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="D34" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="1:6" ht="220.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E35" s="7">
+        <v>42</v>
+      </c>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="D36" s="24">
+        <v>2026</v>
+      </c>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+    </row>
+    <row r="37" spans="1:6" ht="173.25" x14ac:dyDescent="0.25">
+      <c r="A37" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="C37" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="D37" s="26">
+        <v>2026</v>
+      </c>
+      <c r="E37" s="26">
+        <v>84</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C36" r:id="rId1" display="https://link.springer.com/journal/11356"/>
+    <hyperlink ref="H10" r:id="rId2" display="https://doi.org/10.1061/(ASCE)CF.1943-5509.0001214"/>
+    <hyperlink ref="H9" r:id="rId3" display="http://dx.doi.org/10.1016/j.soildyn.2017.06.024"/>
+    <hyperlink ref="H2" r:id="rId4" display="http://dx.doi.org/10.1016/j.engstruct.2007.03.015"/>
+    <hyperlink ref="H6" r:id="rId5" display="http://dx.doi.org/10.1016/j.soildyn.2011.08.002"/>
+    <hyperlink ref="H4" r:id="rId6" display="http://dx.doi.org/10.1193/1.4000074"/>
+    <hyperlink ref="H8" r:id="rId7" display="http://dx.doi.org/10.1193/042313EQS111M"/>
+    <hyperlink ref="H11" r:id="rId8" display="https://doi.org/10.1061/(ASCE)ST.1943-541X.0002590"/>
+    <hyperlink ref="H15" r:id="rId9" display="https://doi.org/10.1080/13632469.2020.1778587"/>
+    <hyperlink ref="H12" r:id="rId10" display="https://doi.org/10.1061/(ASCE)PS.1949-1204.0000590"/>
+    <hyperlink ref="H13" r:id="rId11" display="https://doi.org/10.1115/1.4054686"/>
+    <hyperlink ref="H18" r:id="rId12" display="https://doi.org/10.12989/smm.2023.10.1.063"/>
+    <hyperlink ref="H17" r:id="rId13" tooltip="Persistent link using digital object identifier" display="https://doi.org/10.1016/j.jcsr.2023.108099"/>
+    <hyperlink ref="H16" r:id="rId14" display="https://doi.org/10.1016/j.jobe.2023.107504"/>
+    <hyperlink ref="H19" r:id="rId15" display="https://doi.org/10.1016/j.istruc.2023.06.121"/>
+    <hyperlink ref="H14" r:id="rId16" display="https://doi.org/10.12989/eas.2022.22.2.121"/>
+    <hyperlink ref="H22" r:id="rId17" tooltip="Persistent link using digital object identifier" display="https://doi.org/10.1016/j.istruc.2024.107532"/>
+    <hyperlink ref="H25" r:id="rId18" display="https://doi.org/10.1061/JMCEE7.MTENG-19481"/>
+    <hyperlink ref="H27" r:id="rId19"/>
+    <hyperlink ref="H29" r:id="rId20" tooltip="Persistent link using digital object identifier"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1046,6 +3847,448 @@
       </c>
       <c r="H1" s="1" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="210" x14ac:dyDescent="0.25">
+      <c r="A2" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" s="42">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="195" x14ac:dyDescent="0.25">
+      <c r="A3" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" s="45">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="180" x14ac:dyDescent="0.25">
+      <c r="A4" s="42" t="s">
+        <v>206</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="E4" s="42">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" s="45">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="42" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>213</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>266</v>
+      </c>
+      <c r="E6" s="42">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>215</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="D7" s="45" t="s">
+        <v>266</v>
+      </c>
+      <c r="E7" s="45">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A8" s="49" t="s">
+        <v>216</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>217</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>210</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>266</v>
+      </c>
+      <c r="E8" s="42">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="44" t="s">
+        <v>218</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="D9" s="45" t="s">
+        <v>266</v>
+      </c>
+      <c r="E9" s="45">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="42" t="s">
+        <v>220</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>266</v>
+      </c>
+      <c r="E10" s="42">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A11" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="B11" s="47" t="s">
+        <v>224</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>266</v>
+      </c>
+      <c r="E11" s="45">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>226</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>266</v>
+      </c>
+      <c r="E12" s="42">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+      <c r="A13" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>227</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="D13" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="E13" s="45">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="210" x14ac:dyDescent="0.25">
+      <c r="A14" s="49" t="s">
+        <v>229</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="D14" s="42" t="s">
+        <v>268</v>
+      </c>
+      <c r="E14" s="42">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="195" x14ac:dyDescent="0.25">
+      <c r="A15" s="45" t="s">
+        <v>232</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>233</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>269</v>
+      </c>
+      <c r="E15" s="45">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="180" x14ac:dyDescent="0.25">
+      <c r="A16" s="50" t="s">
+        <v>235</v>
+      </c>
+      <c r="B16" s="51" t="s">
+        <v>236</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="D16" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E16" s="51">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A17" s="50" t="s">
+        <v>238</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>239</v>
+      </c>
+      <c r="C17" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E17" s="51">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A18" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>241</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="D18" s="42" t="s">
+        <v>271</v>
+      </c>
+      <c r="E18" s="42">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A19" s="53" t="s">
+        <v>243</v>
+      </c>
+      <c r="B19" s="45" t="s">
+        <v>244</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="D19" s="45" t="s">
+        <v>268</v>
+      </c>
+      <c r="E19" s="45">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A20" s="54" t="s">
+        <v>246</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="D20" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="E20" s="42">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A21" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="B21" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>251</v>
+      </c>
+      <c r="D21" s="45" t="s">
+        <v>273</v>
+      </c>
+      <c r="E21" s="45">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A22" s="42" t="s">
+        <v>252</v>
+      </c>
+      <c r="B22" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="D22" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="E22" s="42">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A23" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="B23" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="C23" s="46" t="s">
+        <v>251</v>
+      </c>
+      <c r="D23" s="45" t="s">
+        <v>273</v>
+      </c>
+      <c r="E23" s="45">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A24" s="42" t="s">
+        <v>256</v>
+      </c>
+      <c r="B24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="C24" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="D24" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="E24" s="42">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A25" s="44" t="s">
+        <v>258</v>
+      </c>
+      <c r="B25" s="45" t="s">
+        <v>259</v>
+      </c>
+      <c r="C25" s="45" t="s">
+        <v>260</v>
+      </c>
+      <c r="D25" s="45" t="s">
+        <v>274</v>
+      </c>
+      <c r="E25" s="45">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A26" s="49" t="s">
+        <v>258</v>
+      </c>
+      <c r="B26" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="C26" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="D26" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="E26" s="42">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A27" s="44" t="s">
+        <v>258</v>
+      </c>
+      <c r="B27" s="45" t="s">
+        <v>263</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="D27" s="45" t="s">
+        <v>276</v>
+      </c>
+      <c r="E27" s="45">
+        <v>2006</v>
       </c>
     </row>
   </sheetData>

--- a/Academic_CV_Structure_Template.xlsx
+++ b/Academic_CV_Structure_Template.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my-CV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AcademicCV\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" firstSheet="2" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Personal_Info" sheetId="1" r:id="rId1"/>
@@ -56,9 +56,6 @@
     <t>Department</t>
   </si>
   <si>
-    <t>Civil Engineering</t>
-  </si>
-  <si>
     <t>Institution</t>
   </si>
   <si>
@@ -1693,6 +1690,9 @@
   </si>
   <si>
     <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>School of Infrastructure</t>
   </si>
 </sst>
 </file>
@@ -2423,67 +2423,67 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
         <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
         <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -2504,16 +2504,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2534,16 +2534,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2564,16 +2564,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2594,19 +2594,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2627,16 +2627,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2657,19 +2657,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -2692,22 +2692,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2730,22 +2730,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2771,45 +2771,45 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="D2" s="3">
         <v>2005</v>
@@ -2819,13 +2819,13 @@
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H2" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="I2" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="J2" s="3">
         <v>4.4710000000000001</v>
@@ -2833,13 +2833,13 @@
     </row>
     <row r="3" spans="1:10" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D3" s="5">
         <v>2005</v>
@@ -2849,11 +2849,11 @@
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J3" s="5">
         <v>1.169</v>
@@ -2861,13 +2861,13 @@
     </row>
     <row r="4" spans="1:10" ht="252" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>76</v>
       </c>
       <c r="D4" s="8">
         <v>2006</v>
@@ -2877,13 +2877,13 @@
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H4" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="H4" s="29" t="s">
-        <v>163</v>
-      </c>
       <c r="I4" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J4" s="3">
         <v>3.03</v>
@@ -2891,13 +2891,13 @@
     </row>
     <row r="5" spans="1:10" ht="315" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="D5" s="5">
         <v>2006</v>
@@ -2906,16 +2906,16 @@
         <v>22</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="H5" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H5" s="30" t="s">
-        <v>165</v>
-      </c>
       <c r="I5" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J5" s="5">
         <v>3.528</v>
@@ -2923,13 +2923,13 @@
     </row>
     <row r="6" spans="1:10" ht="315" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D6" s="3">
         <v>2006</v>
@@ -2938,16 +2938,16 @@
         <v>22</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="H6" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="H6" s="29" t="s">
-        <v>167</v>
-      </c>
       <c r="I6" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J6" s="3">
         <v>3.718</v>
@@ -2955,13 +2955,13 @@
     </row>
     <row r="7" spans="1:10" ht="299.25" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="C7" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D7" s="5">
         <v>2006</v>
@@ -2970,16 +2970,16 @@
         <v>22</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G7" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="H7" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="H7" s="31" t="s">
-        <v>169</v>
-      </c>
       <c r="I7" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J7" s="32">
         <v>4.43</v>
@@ -2987,13 +2987,13 @@
     </row>
     <row r="8" spans="1:10" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="C8" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D8" s="3">
         <v>2006</v>
@@ -3003,13 +3003,13 @@
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="H8" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="H8" s="33" t="s">
-        <v>171</v>
-      </c>
       <c r="I8" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J8" s="34">
         <v>3.03</v>
@@ -3017,13 +3017,13 @@
     </row>
     <row r="9" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D9" s="5">
         <v>2008</v>
@@ -3035,13 +3035,13 @@
         <v>3</v>
       </c>
       <c r="G9" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="H9" s="35" t="s">
         <v>172</v>
       </c>
-      <c r="H9" s="35" t="s">
-        <v>173</v>
-      </c>
       <c r="I9" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J9" s="5">
         <v>3.718</v>
@@ -3049,13 +3049,13 @@
     </row>
     <row r="10" spans="1:10" ht="189" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="D10" s="3">
         <v>2008</v>
@@ -3067,13 +3067,13 @@
         <v>1</v>
       </c>
       <c r="G10" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="H10" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="H10" s="28" t="s">
-        <v>175</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J10" s="34">
         <v>2.3719999999999999</v>
@@ -3081,13 +3081,13 @@
     </row>
     <row r="11" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="C11" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D11" s="5">
         <v>2012</v>
@@ -3099,13 +3099,13 @@
         <v>10</v>
       </c>
       <c r="G11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="H11" s="35" t="s">
         <v>176</v>
       </c>
-      <c r="H11" s="35" t="s">
-        <v>177</v>
-      </c>
       <c r="I11" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J11" s="5">
         <v>3.3119999999999998</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="12" spans="1:10" ht="189" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="C12" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D12" s="3">
         <v>2012</v>
@@ -3131,13 +3131,13 @@
         <v>3</v>
       </c>
       <c r="G12" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="H12" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="H12" s="28" t="s">
-        <v>179</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J12" s="3">
         <v>1.952</v>
@@ -3145,13 +3145,13 @@
     </row>
     <row r="13" spans="1:10" ht="204.75" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="D13" s="5">
         <v>2012</v>
@@ -3164,10 +3164,10 @@
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J13" s="5">
         <v>1.0509999999999999</v>
@@ -3175,13 +3175,13 @@
     </row>
     <row r="14" spans="1:10" ht="126" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="D14" s="3">
         <v>2012</v>
@@ -3193,13 +3193,13 @@
         <v>1</v>
       </c>
       <c r="G14" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="H14" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="H14" s="28" t="s">
-        <v>182</v>
-      </c>
       <c r="I14" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J14" s="34">
         <v>2.0179999999999998</v>
@@ -3207,13 +3207,13 @@
     </row>
     <row r="15" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="C15" s="13" t="s">
         <v>100</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>101</v>
       </c>
       <c r="D15" s="7">
         <v>2014</v>
@@ -3225,13 +3225,13 @@
         <v>2</v>
       </c>
       <c r="G15" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="H15" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="H15" s="37" t="s">
-        <v>184</v>
-      </c>
       <c r="I15" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J15" s="32">
         <v>3.9940000000000002</v>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="16" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>103</v>
-      </c>
       <c r="C16" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D16" s="2">
         <v>2015</v>
@@ -3258,10 +3258,10 @@
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="28" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J16" s="34">
         <v>5.3179999999999996</v>
@@ -3269,13 +3269,13 @@
     </row>
     <row r="17" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="C17" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D17" s="7">
         <v>2017</v>
@@ -3286,10 +3286,10 @@
       <c r="F17" s="16"/>
       <c r="G17" s="7"/>
       <c r="H17" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J17" s="32">
         <v>3.6459999999999999</v>
@@ -3297,13 +3297,13 @@
     </row>
     <row r="18" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="C18" s="17" t="s">
         <v>107</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>108</v>
       </c>
       <c r="D18" s="2">
         <v>2018</v>
@@ -3315,13 +3315,13 @@
         <v>6</v>
       </c>
       <c r="G18" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H18" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="H18" s="28" t="s">
-        <v>188</v>
-      </c>
       <c r="I18" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J18" s="34">
         <v>1.825</v>
@@ -3329,13 +3329,13 @@
     </row>
     <row r="19" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="C19" s="19" t="s">
         <v>110</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>111</v>
       </c>
       <c r="D19" s="20">
         <v>2020</v>
@@ -3348,10 +3348,10 @@
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="37" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J19" s="32">
         <v>2.9830000000000001</v>
@@ -3359,13 +3359,13 @@
     </row>
     <row r="20" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="21" t="s">
         <v>113</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>114</v>
       </c>
       <c r="D20" s="2">
         <v>2021</v>
@@ -3377,25 +3377,25 @@
         <v>4</v>
       </c>
       <c r="G20" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="I20" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J20" s="34"/>
     </row>
     <row r="21" spans="1:10" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="18" t="s">
         <v>115</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>116</v>
       </c>
       <c r="D21" s="7">
         <v>2022</v>
@@ -3408,10 +3408,10 @@
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J21" s="32">
         <v>1.952</v>
@@ -3419,13 +3419,13 @@
     </row>
     <row r="22" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="C22" s="21" t="s">
         <v>118</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>119</v>
       </c>
       <c r="D22" s="2">
         <v>2022</v>
@@ -3438,22 +3438,22 @@
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J22" s="34"/>
     </row>
     <row r="23" spans="1:10" ht="220.5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="C23" s="7" t="s">
         <v>121</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>122</v>
       </c>
       <c r="D23" s="7">
         <v>2022</v>
@@ -3466,22 +3466,22 @@
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J23" s="32"/>
     </row>
     <row r="24" spans="1:10" ht="236.25" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="21" t="s">
         <v>124</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>125</v>
       </c>
       <c r="D24" s="2">
         <v>2023</v>
@@ -3494,22 +3494,22 @@
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J24" s="34"/>
     </row>
     <row r="25" spans="1:10" ht="189" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="C25" s="22" t="s">
         <v>127</v>
-      </c>
-      <c r="C25" s="22" t="s">
-        <v>128</v>
       </c>
       <c r="D25" s="7">
         <v>2023</v>
@@ -3520,20 +3520,20 @@
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
       <c r="H25" s="39" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="32"/>
     </row>
     <row r="26" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="C26" s="21" t="s">
         <v>130</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>131</v>
       </c>
       <c r="D26" s="14">
         <v>2023</v>
@@ -3546,20 +3546,20 @@
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="38" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="34"/>
     </row>
     <row r="27" spans="1:10" ht="252" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="C27" s="22" t="s">
         <v>133</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>134</v>
       </c>
       <c r="D27" s="7">
         <v>2023</v>
@@ -3570,22 +3570,22 @@
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="39" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J27" s="32"/>
     </row>
     <row r="28" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="C28" s="21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D28" s="2">
         <v>2024</v>
@@ -3598,22 +3598,22 @@
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="40" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I28" s="24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J28" s="34"/>
     </row>
     <row r="29" spans="1:10" ht="220.5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D29" s="7">
         <v>2024</v>
@@ -3626,10 +3626,10 @@
       </c>
       <c r="G29" s="26"/>
       <c r="H29" s="39" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J29" s="41">
         <v>3.5</v>
@@ -3637,13 +3637,13 @@
     </row>
     <row r="30" spans="1:10" ht="126" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D30" s="2">
         <v>2024</v>
@@ -3655,13 +3655,13 @@
     </row>
     <row r="31" spans="1:10" ht="299.25" x14ac:dyDescent="0.25">
       <c r="A31" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>140</v>
-      </c>
       <c r="C31" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D31" s="7">
         <v>2024</v>
@@ -3673,13 +3673,13 @@
     </row>
     <row r="32" spans="1:10" ht="236.25" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C32" s="15" t="s">
         <v>141</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>142</v>
       </c>
       <c r="D32" s="2">
         <v>2025</v>
@@ -3693,13 +3693,13 @@
     </row>
     <row r="33" spans="1:6" ht="220.5" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="C33" s="22" t="s">
         <v>144</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>145</v>
       </c>
       <c r="D33" s="7">
         <v>2025</v>
@@ -3713,13 +3713,13 @@
     </row>
     <row r="34" spans="1:6" ht="283.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="21" t="s">
         <v>147</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>148</v>
       </c>
       <c r="D34" s="2">
         <v>2026</v>
@@ -3729,13 +3729,13 @@
     </row>
     <row r="35" spans="1:6" ht="220.5" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D35" s="7">
         <v>2026</v>
@@ -3747,13 +3747,13 @@
     </row>
     <row r="36" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="21" t="s">
         <v>151</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>152</v>
       </c>
       <c r="D36" s="24">
         <v>2026</v>
@@ -3763,13 +3763,13 @@
     </row>
     <row r="37" spans="1:6" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="B37" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="C37" s="27" t="s">
         <v>154</v>
-      </c>
-      <c r="C37" s="27" t="s">
-        <v>155</v>
       </c>
       <c r="D37" s="26">
         <v>2026</v>
@@ -3778,7 +3778,7 @@
         <v>84</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -3825,42 +3825,42 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="B2" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="C2" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="C2" s="43" t="s">
-        <v>203</v>
-      </c>
       <c r="D2" s="42" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E2" s="42">
         <v>2024</v>
@@ -3868,16 +3868,16 @@
     </row>
     <row r="3" spans="1:8" ht="195" x14ac:dyDescent="0.25">
       <c r="A3" s="44" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" s="45" t="s">
         <v>204</v>
       </c>
-      <c r="B3" s="45" t="s">
-        <v>205</v>
-      </c>
       <c r="C3" s="46" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E3" s="45">
         <v>2024</v>
@@ -3885,16 +3885,16 @@
     </row>
     <row r="4" spans="1:8" ht="180" x14ac:dyDescent="0.25">
       <c r="A4" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="B4" s="42" t="s">
-        <v>207</v>
-      </c>
       <c r="C4" s="43" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D4" s="42" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E4" s="42">
         <v>2024</v>
@@ -3902,16 +3902,16 @@
     </row>
     <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" s="47" t="s">
         <v>208</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="C5" s="46" t="s">
         <v>209</v>
       </c>
-      <c r="C5" s="46" t="s">
-        <v>210</v>
-      </c>
       <c r="D5" s="45" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E5" s="45">
         <v>2024</v>
@@ -3919,16 +3919,16 @@
     </row>
     <row r="6" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="B6" s="48" t="s">
         <v>211</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="C6" s="43" t="s">
         <v>212</v>
       </c>
-      <c r="C6" s="43" t="s">
-        <v>213</v>
-      </c>
       <c r="D6" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E6" s="42">
         <v>2024</v>
@@ -3936,16 +3936,16 @@
     </row>
     <row r="7" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="44" t="s">
+        <v>213</v>
+      </c>
+      <c r="B7" s="47" t="s">
         <v>214</v>
       </c>
-      <c r="B7" s="47" t="s">
-        <v>215</v>
-      </c>
       <c r="C7" s="46" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D7" s="45" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E7" s="45">
         <v>2024</v>
@@ -3953,16 +3953,16 @@
     </row>
     <row r="8" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
+        <v>215</v>
+      </c>
+      <c r="B8" s="48" t="s">
         <v>216</v>
       </c>
-      <c r="B8" s="48" t="s">
-        <v>217</v>
-      </c>
       <c r="C8" s="43" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E8" s="42">
         <v>2024</v>
@@ -3970,16 +3970,16 @@
     </row>
     <row r="9" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="44" t="s">
+        <v>217</v>
+      </c>
+      <c r="B9" s="47" t="s">
         <v>218</v>
       </c>
-      <c r="B9" s="47" t="s">
-        <v>219</v>
-      </c>
       <c r="C9" s="46" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D9" s="45" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E9" s="45">
         <v>2024</v>
@@ -3987,16 +3987,16 @@
     </row>
     <row r="10" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="B10" s="48" t="s">
         <v>220</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="C10" s="43" t="s">
         <v>221</v>
       </c>
-      <c r="C10" s="43" t="s">
-        <v>222</v>
-      </c>
       <c r="D10" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E10" s="42">
         <v>2024</v>
@@ -4004,16 +4004,16 @@
     </row>
     <row r="11" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="45" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" s="47" t="s">
         <v>223</v>
       </c>
-      <c r="B11" s="47" t="s">
-        <v>224</v>
-      </c>
       <c r="C11" s="46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D11" s="45" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E11" s="45">
         <v>2024</v>
@@ -4021,16 +4021,16 @@
     </row>
     <row r="12" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="42" t="s">
+        <v>224</v>
+      </c>
+      <c r="B12" s="48" t="s">
         <v>225</v>
       </c>
-      <c r="B12" s="48" t="s">
-        <v>226</v>
-      </c>
       <c r="C12" s="43" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E12" s="42">
         <v>2024</v>
@@ -4038,16 +4038,16 @@
     </row>
     <row r="13" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A13" s="45" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="C13" s="46" t="s">
         <v>227</v>
       </c>
-      <c r="C13" s="46" t="s">
-        <v>228</v>
-      </c>
       <c r="D13" s="55" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E13" s="45">
         <v>2023</v>
@@ -4055,16 +4055,16 @@
     </row>
     <row r="14" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A14" s="49" t="s">
+        <v>228</v>
+      </c>
+      <c r="B14" s="42" t="s">
         <v>229</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="C14" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="C14" s="43" t="s">
-        <v>231</v>
-      </c>
       <c r="D14" s="42" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E14" s="42">
         <v>2022</v>
@@ -4072,16 +4072,16 @@
     </row>
     <row r="15" spans="1:8" ht="195" x14ac:dyDescent="0.25">
       <c r="A15" s="45" t="s">
+        <v>231</v>
+      </c>
+      <c r="B15" s="45" t="s">
         <v>232</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="C15" s="46" t="s">
         <v>233</v>
       </c>
-      <c r="C15" s="46" t="s">
-        <v>234</v>
-      </c>
       <c r="D15" s="45" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E15" s="45">
         <v>2022</v>
@@ -4089,16 +4089,16 @@
     </row>
     <row r="16" spans="1:8" ht="180" x14ac:dyDescent="0.25">
       <c r="A16" s="50" t="s">
+        <v>234</v>
+      </c>
+      <c r="B16" s="51" t="s">
         <v>235</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="C16" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C16" s="52" t="s">
-        <v>237</v>
-      </c>
       <c r="D16" s="51" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E16" s="51">
         <v>2022</v>
@@ -4106,16 +4106,16 @@
     </row>
     <row r="17" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A17" s="50" t="s">
+        <v>237</v>
+      </c>
+      <c r="B17" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="B17" s="51" t="s">
-        <v>239</v>
-      </c>
       <c r="C17" s="52" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E17" s="51">
         <v>2022</v>
@@ -4123,16 +4123,16 @@
     </row>
     <row r="18" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A18" s="42" t="s">
+        <v>239</v>
+      </c>
+      <c r="B18" s="42" t="s">
         <v>240</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="C18" s="43" t="s">
         <v>241</v>
       </c>
-      <c r="C18" s="43" t="s">
-        <v>242</v>
-      </c>
       <c r="D18" s="42" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E18" s="42">
         <v>2019</v>
@@ -4140,16 +4140,16 @@
     </row>
     <row r="19" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="53" t="s">
+        <v>242</v>
+      </c>
+      <c r="B19" s="45" t="s">
         <v>243</v>
       </c>
-      <c r="B19" s="45" t="s">
+      <c r="C19" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="C19" s="45" t="s">
-        <v>245</v>
-      </c>
       <c r="D19" s="45" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E19" s="45">
         <v>2017</v>
@@ -4157,16 +4157,16 @@
     </row>
     <row r="20" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A20" s="54" t="s">
+        <v>245</v>
+      </c>
+      <c r="B20" s="42" t="s">
         <v>246</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="C20" s="43" t="s">
         <v>247</v>
       </c>
-      <c r="C20" s="43" t="s">
-        <v>248</v>
-      </c>
       <c r="D20" s="42" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E20" s="42">
         <v>2017</v>
@@ -4174,16 +4174,16 @@
     </row>
     <row r="21" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A21" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="B21" s="45" t="s">
         <v>249</v>
       </c>
-      <c r="B21" s="45" t="s">
+      <c r="C21" s="46" t="s">
         <v>250</v>
       </c>
-      <c r="C21" s="46" t="s">
-        <v>251</v>
-      </c>
       <c r="D21" s="45" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E21" s="45">
         <v>2012</v>
@@ -4191,16 +4191,16 @@
     </row>
     <row r="22" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A22" s="42" t="s">
+        <v>251</v>
+      </c>
+      <c r="B22" s="42" t="s">
         <v>252</v>
       </c>
-      <c r="B22" s="42" t="s">
-        <v>253</v>
-      </c>
       <c r="C22" s="43" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D22" s="42" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E22" s="42">
         <v>2012</v>
@@ -4208,16 +4208,16 @@
     </row>
     <row r="23" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A23" s="45" t="s">
+        <v>253</v>
+      </c>
+      <c r="B23" s="45" t="s">
         <v>254</v>
       </c>
-      <c r="B23" s="45" t="s">
-        <v>255</v>
-      </c>
       <c r="C23" s="46" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D23" s="45" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E23" s="45">
         <v>2012</v>
@@ -4225,16 +4225,16 @@
     </row>
     <row r="24" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A24" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="B24" s="42" t="s">
         <v>256</v>
       </c>
-      <c r="B24" s="42" t="s">
-        <v>257</v>
-      </c>
       <c r="C24" s="43" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D24" s="42" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E24" s="42">
         <v>2012</v>
@@ -4242,16 +4242,16 @@
     </row>
     <row r="25" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A25" s="44" t="s">
+        <v>257</v>
+      </c>
+      <c r="B25" s="45" t="s">
         <v>258</v>
       </c>
-      <c r="B25" s="45" t="s">
+      <c r="C25" s="45" t="s">
         <v>259</v>
       </c>
-      <c r="C25" s="45" t="s">
-        <v>260</v>
-      </c>
       <c r="D25" s="45" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E25" s="45">
         <v>2010</v>
@@ -4259,16 +4259,16 @@
     </row>
     <row r="26" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A26" s="49" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B26" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="C26" s="43" t="s">
         <v>261</v>
       </c>
-      <c r="C26" s="43" t="s">
-        <v>262</v>
-      </c>
       <c r="D26" s="42" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E26" s="42">
         <v>2008</v>
@@ -4276,16 +4276,16 @@
     </row>
     <row r="27" spans="1:5" ht="165" x14ac:dyDescent="0.25">
       <c r="A27" s="44" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B27" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="C27" s="46" t="s">
         <v>263</v>
       </c>
-      <c r="C27" s="46" t="s">
-        <v>264</v>
-      </c>
       <c r="D27" s="45" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E27" s="45">
         <v>2006</v>
@@ -4310,22 +4310,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -4348,22 +4348,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -4385,19 +4385,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -4418,19 +4418,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Academic_CV_Structure_Template.xlsx
+++ b/Academic_CV_Structure_Template.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Personal_Info" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="246">
   <si>
     <t>Field</t>
   </si>
@@ -147,12 +147,6 @@
   </si>
   <si>
     <t>DOI</t>
-  </si>
-  <si>
-    <t>SCI/Scopus</t>
-  </si>
-  <si>
-    <t>Impact_Factor</t>
   </si>
   <si>
     <t>Conference</t>
@@ -869,133 +863,46 @@
     <t>174-182</t>
   </si>
   <si>
-    <t>DOI: 10.1016/j.engstruct.2007.03.015</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>1437-1446</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>1117–1145</t>
   </si>
   <si>
-    <t>DOI: 10.1193/1.4000074</t>
-  </si>
-  <si>
     <t>99-111</t>
   </si>
   <si>
-    <t>DOI: 10.1080/19475705.2011.647336</t>
-  </si>
-  <si>
     <t>42-55</t>
   </si>
   <si>
-    <t>DOI: 10.1016/j.soildyn.2011.08.002</t>
-  </si>
-  <si>
     <t>205-223</t>
   </si>
   <si>
-    <t>DOI: 10.1002/eqe.2338</t>
-  </si>
-  <si>
     <t>1427-1449</t>
   </si>
   <si>
-    <t>DOI: 10.1193/042313EQS111M.</t>
-  </si>
-  <si>
     <t>480–491</t>
   </si>
   <si>
-    <t>DOI: 10.1016/j.soildyn.2017.06.024</t>
-  </si>
-  <si>
     <t>04018083(1-18)</t>
   </si>
   <si>
-    <t>DOI: 10.1061/(ASCE)CF.1943-5509.0001214</t>
-  </si>
-  <si>
     <t>04020048(1-12)</t>
   </si>
   <si>
-    <t>DOI: 10.1061/(ASCE)ST.1943-541X.0002590</t>
-  </si>
-  <si>
     <t>04021053 (1-30)</t>
   </si>
   <si>
-    <t>DOI: 10.1061/(ASCE)PS.1949-1204.0000590</t>
-  </si>
-  <si>
-    <t>DOI: 10.1115/1.4054686</t>
-  </si>
-  <si>
     <t>121-135</t>
   </si>
   <si>
-    <t>DOI: 10.12989/eas.2022.22.2.121</t>
-  </si>
-  <si>
     <t>2911-2926</t>
   </si>
   <si>
-    <t>DOI: 10.1080/13632469.2020.1778587</t>
-  </si>
-  <si>
-    <t>DOI: 10.1016/j.jobe.2023.107504</t>
-  </si>
-  <si>
-    <t>DOI: 10.1016/j.jcsr.2023.108099</t>
-  </si>
-  <si>
     <t>63-86</t>
   </si>
   <si>
-    <t>DOI: 10.12989/smm.2023.10.1.063</t>
-  </si>
-  <si>
-    <t>DOI: 10.1016/j.istruc.2023.06.121</t>
-  </si>
-  <si>
     <t>4323–4362</t>
-  </si>
-  <si>
-    <t>DOI: 10.1080/13632469.2024.2376625</t>
-  </si>
-  <si>
-    <t>DOI: 10.1061/JPSEA2.PSENG-1480</t>
-  </si>
-  <si>
-    <t>DOI: 10.1016/j.istruc.2024.107532</t>
-  </si>
-  <si>
-    <t>DOI: 10.1016/j.istruc.2024.107643</t>
-  </si>
-  <si>
-    <t>DOI: 10.1142/S0219455425300022</t>
-  </si>
-  <si>
-    <t>DOI: 10.1061/JMCEE7.MTENG-19481</t>
-  </si>
-  <si>
-    <t>DOI: 10.1007/s10518-026-02439-3</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1002/esp4.70000</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s11356-026-37674-3</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.probengmech.2026.103935</t>
   </si>
   <si>
     <t>Pandit, U.K., Jibhakate, D., Mondal, G. and Punera, D.</t>
@@ -1699,7 +1606,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1798,38 +1705,10 @@
       <name val="Times New Roman"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color rgb="FF0000FF"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF222222"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1892,7 +1771,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1941,25 +1820,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2020,43 +1885,21 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2065,28 +1908,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2423,7 +2265,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>276</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2504,7 +2346,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>7</v>
@@ -2534,16 +2376,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2564,13 +2406,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>24</v>
@@ -2597,7 +2439,7 @@
         <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>29</v>
@@ -2606,7 +2448,7 @@
         <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2630,10 +2472,10 @@
         <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>24</v>
@@ -2657,19 +2499,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2755,7 +2597,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2764,12 +2606,9 @@
     <col min="4" max="4" width="9" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
@@ -2791,25 +2630,16 @@
       <c r="G1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="D2" s="3">
         <v>2005</v>
@@ -2819,27 +2649,18 @@
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H2" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J2" s="3">
-        <v>4.4710000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="110.25" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="D3" s="5">
         <v>2005</v>
@@ -2849,25 +2670,18 @@
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1.169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="252" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="252" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>75</v>
       </c>
       <c r="D4" s="8">
         <v>2006</v>
@@ -2877,27 +2691,18 @@
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H4" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J4" s="3">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="315" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="315" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="D5" s="5">
         <v>2006</v>
@@ -2906,30 +2711,21 @@
         <v>22</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="315" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="H5" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="J5" s="5">
-        <v>3.528</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="315" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D6" s="3">
         <v>2006</v>
@@ -2938,30 +2734,21 @@
         <v>22</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="I6" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="J6" s="3">
-        <v>3.718</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="299.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" ht="299.25" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D7" s="5">
         <v>2006</v>
@@ -2970,30 +2757,21 @@
         <v>22</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="H7" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J7" s="32">
-        <v>4.43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="173.25" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D8" s="3">
         <v>2006</v>
@@ -3003,27 +2781,18 @@
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="H8" s="33" t="s">
-        <v>170</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="J8" s="34">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D9" s="5">
         <v>2008</v>
@@ -3035,27 +2804,18 @@
         <v>3</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="H9" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J9" s="5">
-        <v>3.718</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="189" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="189" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D10" s="3">
         <v>2008</v>
@@ -3066,28 +2826,19 @@
       <c r="F10" s="2">
         <v>1</v>
       </c>
-      <c r="G10" s="36" t="s">
-        <v>173</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="J10" s="34">
-        <v>2.3719999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="28" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D11" s="5">
         <v>2012</v>
@@ -3099,27 +2850,18 @@
         <v>10</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="H11" s="35" t="s">
-        <v>176</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J11" s="5">
-        <v>3.3119999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="189" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="189" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D12" s="3">
         <v>2012</v>
@@ -3131,27 +2873,18 @@
         <v>3</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1.952</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="204.75" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="204.75" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="D13" s="5">
         <v>2012</v>
@@ -3163,25 +2896,16 @@
         <v>2</v>
       </c>
       <c r="G13" s="7"/>
-      <c r="H13" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J13" s="5">
-        <v>1.0509999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="126" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:7" ht="126" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D14" s="3">
         <v>2012</v>
@@ -3193,27 +2917,18 @@
         <v>1</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="H14" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="J14" s="34">
-        <v>2.0179999999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="63" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>98</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>100</v>
       </c>
       <c r="D15" s="7">
         <v>2014</v>
@@ -3225,27 +2940,18 @@
         <v>2</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H15" s="37" t="s">
-        <v>183</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J15" s="32">
-        <v>3.9940000000000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="63" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D16" s="2">
         <v>2015</v>
@@ -3257,25 +2963,16 @@
         <v>3</v>
       </c>
       <c r="G16" s="2"/>
-      <c r="H16" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="J16" s="34">
-        <v>5.3179999999999996</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D17" s="7">
         <v>2017</v>
@@ -3285,25 +2982,16 @@
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="35" t="s">
-        <v>185</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J17" s="32">
-        <v>3.6459999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:7" ht="63" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="17" t="s">
         <v>105</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>107</v>
       </c>
       <c r="D18" s="2">
         <v>2018</v>
@@ -3315,27 +3003,18 @@
         <v>6</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="H18" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="J18" s="34">
-        <v>1.825</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>108</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>110</v>
       </c>
       <c r="D19" s="20">
         <v>2020</v>
@@ -3347,25 +3026,16 @@
         <v>5</v>
       </c>
       <c r="G19" s="7"/>
-      <c r="H19" s="37" t="s">
-        <v>188</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J19" s="32">
-        <v>2.9830000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:7" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="21" t="s">
         <v>111</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>113</v>
       </c>
       <c r="D20" s="2">
         <v>2021</v>
@@ -3376,26 +3046,19 @@
       <c r="F20" s="2">
         <v>4</v>
       </c>
-      <c r="G20" s="38" t="s">
-        <v>189</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="J20" s="34"/>
-    </row>
-    <row r="21" spans="1:10" ht="173.25" x14ac:dyDescent="0.25">
+      <c r="G20" s="29" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D21" s="7">
         <v>2022</v>
@@ -3407,25 +3070,16 @@
         <v>5</v>
       </c>
       <c r="G21" s="7"/>
-      <c r="H21" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J21" s="32">
-        <v>1.952</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="21" t="s">
         <v>116</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>118</v>
       </c>
       <c r="D22" s="2">
         <v>2022</v>
@@ -3437,23 +3091,16 @@
         <v>2</v>
       </c>
       <c r="G22" s="2"/>
-      <c r="H22" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="J22" s="34"/>
-    </row>
-    <row r="23" spans="1:10" ht="220.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:7" ht="220.5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>121</v>
       </c>
       <c r="D23" s="7">
         <v>2022</v>
@@ -3465,23 +3112,16 @@
         <v>6</v>
       </c>
       <c r="G23" s="7"/>
-      <c r="H23" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J23" s="32"/>
-    </row>
-    <row r="24" spans="1:10" ht="236.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:7" ht="236.25" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="21" t="s">
         <v>122</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>124</v>
       </c>
       <c r="D24" s="2">
         <v>2023</v>
@@ -3493,23 +3133,16 @@
         <v>1</v>
       </c>
       <c r="G24" s="2"/>
-      <c r="H24" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="J24" s="34"/>
-    </row>
-    <row r="25" spans="1:10" ht="189" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:7" ht="189" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="22" t="s">
         <v>125</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="22" t="s">
-        <v>127</v>
       </c>
       <c r="D25" s="7">
         <v>2023</v>
@@ -3519,21 +3152,16 @@
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
-      <c r="H25" s="39" t="s">
-        <v>195</v>
-      </c>
-      <c r="I25" s="7"/>
-      <c r="J25" s="32"/>
-    </row>
-    <row r="26" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="21" t="s">
         <v>128</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>130</v>
       </c>
       <c r="D26" s="14">
         <v>2023</v>
@@ -3545,21 +3173,16 @@
         <v>1</v>
       </c>
       <c r="G26" s="2"/>
-      <c r="H26" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="34"/>
-    </row>
-    <row r="27" spans="1:10" ht="252" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:7" ht="252" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" s="22" t="s">
         <v>131</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>133</v>
       </c>
       <c r="D27" s="7">
         <v>2023</v>
@@ -3569,23 +3192,16 @@
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
-      <c r="H27" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J27" s="32"/>
-    </row>
-    <row r="28" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:7" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D28" s="2">
         <v>2024</v>
@@ -3597,23 +3213,16 @@
         <v>15</v>
       </c>
       <c r="G28" s="2"/>
-      <c r="H28" s="40" t="s">
-        <v>198</v>
-      </c>
-      <c r="I28" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="J28" s="34"/>
-    </row>
-    <row r="29" spans="1:10" ht="220.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:7" ht="220.5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" s="22" t="s">
         <v>111</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>113</v>
       </c>
       <c r="D29" s="7">
         <v>2024</v>
@@ -3625,25 +3234,16 @@
         <v>3</v>
       </c>
       <c r="G29" s="26"/>
-      <c r="H29" s="39" t="s">
-        <v>199</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J29" s="41">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="126" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:7" ht="126" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D30" s="2">
         <v>2024</v>
@@ -3653,15 +3253,15 @@
       </c>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:10" ht="299.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="299.25" x14ac:dyDescent="0.25">
       <c r="A31" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D31" s="7">
         <v>2024</v>
@@ -3671,15 +3271,15 @@
       </c>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="1:10" ht="236.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="236.25" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="C32" s="15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D32" s="2">
         <v>2025</v>
@@ -3693,13 +3293,13 @@
     </row>
     <row r="33" spans="1:6" ht="220.5" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33" s="22" t="s">
         <v>142</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>144</v>
       </c>
       <c r="D33" s="7">
         <v>2025</v>
@@ -3713,13 +3313,13 @@
     </row>
     <row r="34" spans="1:6" ht="283.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>145</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>147</v>
       </c>
       <c r="D34" s="2">
         <v>2026</v>
@@ -3729,13 +3329,13 @@
     </row>
     <row r="35" spans="1:6" ht="220.5" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D35" s="7">
         <v>2026</v>
@@ -3747,13 +3347,13 @@
     </row>
     <row r="36" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>149</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>151</v>
       </c>
       <c r="D36" s="24">
         <v>2026</v>
@@ -3763,13 +3363,13 @@
     </row>
     <row r="37" spans="1:6" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="C37" s="27" t="s">
         <v>152</v>
-      </c>
-      <c r="B37" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="C37" s="27" t="s">
-        <v>154</v>
       </c>
       <c r="D37" s="26">
         <v>2026</v>
@@ -3778,31 +3378,12 @@
         <v>84</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C36" r:id="rId1" display="https://link.springer.com/journal/11356"/>
-    <hyperlink ref="H10" r:id="rId2" display="https://doi.org/10.1061/(ASCE)CF.1943-5509.0001214"/>
-    <hyperlink ref="H9" r:id="rId3" display="http://dx.doi.org/10.1016/j.soildyn.2017.06.024"/>
-    <hyperlink ref="H2" r:id="rId4" display="http://dx.doi.org/10.1016/j.engstruct.2007.03.015"/>
-    <hyperlink ref="H6" r:id="rId5" display="http://dx.doi.org/10.1016/j.soildyn.2011.08.002"/>
-    <hyperlink ref="H4" r:id="rId6" display="http://dx.doi.org/10.1193/1.4000074"/>
-    <hyperlink ref="H8" r:id="rId7" display="http://dx.doi.org/10.1193/042313EQS111M"/>
-    <hyperlink ref="H11" r:id="rId8" display="https://doi.org/10.1061/(ASCE)ST.1943-541X.0002590"/>
-    <hyperlink ref="H15" r:id="rId9" display="https://doi.org/10.1080/13632469.2020.1778587"/>
-    <hyperlink ref="H12" r:id="rId10" display="https://doi.org/10.1061/(ASCE)PS.1949-1204.0000590"/>
-    <hyperlink ref="H13" r:id="rId11" display="https://doi.org/10.1115/1.4054686"/>
-    <hyperlink ref="H18" r:id="rId12" display="https://doi.org/10.12989/smm.2023.10.1.063"/>
-    <hyperlink ref="H17" r:id="rId13" tooltip="Persistent link using digital object identifier" display="https://doi.org/10.1016/j.jcsr.2023.108099"/>
-    <hyperlink ref="H16" r:id="rId14" display="https://doi.org/10.1016/j.jobe.2023.107504"/>
-    <hyperlink ref="H19" r:id="rId15" display="https://doi.org/10.1016/j.istruc.2023.06.121"/>
-    <hyperlink ref="H14" r:id="rId16" display="https://doi.org/10.12989/eas.2022.22.2.121"/>
-    <hyperlink ref="H22" r:id="rId17" tooltip="Persistent link using digital object identifier" display="https://doi.org/10.1016/j.istruc.2024.107532"/>
-    <hyperlink ref="H25" r:id="rId18" display="https://doi.org/10.1061/JMCEE7.MTENG-19481"/>
-    <hyperlink ref="H27" r:id="rId19"/>
-    <hyperlink ref="H29" r:id="rId20" tooltip="Persistent link using digital object identifier"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3831,10 +3412,10 @@
         <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>24</v>
@@ -3846,448 +3427,448 @@
         <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="210" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="E2" s="30">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="195" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="E3" s="33">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="180" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="E4" s="30">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="E5" s="33">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="E6" s="30">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="E7" s="33">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="E8" s="30">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="E9" s="33">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="E10" s="30">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A11" s="33" t="s">
+        <v>191</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="E11" s="33">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="B12" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="E12" s="30">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" s="33">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="210" x14ac:dyDescent="0.25">
+      <c r="A14" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="E14" s="30">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="195" x14ac:dyDescent="0.25">
+      <c r="A15" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B15" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C15" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="D2" s="42" t="s">
-        <v>264</v>
-      </c>
-      <c r="E2" s="42">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="195" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
+      <c r="D15" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" s="33">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="180" x14ac:dyDescent="0.25">
+      <c r="A16" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B16" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="C3" s="46" t="s">
-        <v>202</v>
-      </c>
-      <c r="D3" s="45" t="s">
-        <v>264</v>
-      </c>
-      <c r="E3" s="45">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="180" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
+      <c r="C16" s="40" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="D16" s="39" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="39">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>264</v>
-      </c>
-      <c r="E4" s="42">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
+      <c r="B17" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="C17" s="40" t="s">
+        <v>205</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>238</v>
+      </c>
+      <c r="E17" s="39">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A18" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="B18" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="D5" s="45" t="s">
-        <v>265</v>
-      </c>
-      <c r="E5" s="45">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="s">
+      <c r="C18" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="D18" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="E18" s="30">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A19" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="B19" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="D6" s="42" t="s">
-        <v>265</v>
-      </c>
-      <c r="E6" s="42">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+      <c r="C19" s="33" t="s">
         <v>213</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="D19" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="E19" s="33">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A20" s="42" t="s">
         <v>214</v>
       </c>
-      <c r="C7" s="46" t="s">
-        <v>209</v>
-      </c>
-      <c r="D7" s="45" t="s">
-        <v>265</v>
-      </c>
-      <c r="E7" s="45">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="90" x14ac:dyDescent="0.25">
-      <c r="A8" s="49" t="s">
+      <c r="B20" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="C20" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="C8" s="43" t="s">
-        <v>209</v>
-      </c>
-      <c r="D8" s="42" t="s">
-        <v>265</v>
-      </c>
-      <c r="E8" s="42">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
+      <c r="D20" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="E20" s="30">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A21" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="B21" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="C9" s="46" t="s">
-        <v>209</v>
-      </c>
-      <c r="D9" s="45" t="s">
-        <v>265</v>
-      </c>
-      <c r="E9" s="45">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="90" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
+      <c r="C21" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="D21" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="E21" s="33">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A22" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="B22" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="D10" s="42" t="s">
-        <v>265</v>
-      </c>
-      <c r="E10" s="42">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A11" s="45" t="s">
+      <c r="C22" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="E22" s="30">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A23" s="33" t="s">
         <v>222</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="B23" s="33" t="s">
         <v>223</v>
       </c>
-      <c r="C11" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="D11" s="45" t="s">
-        <v>265</v>
-      </c>
-      <c r="E11" s="45">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A12" s="42" t="s">
+      <c r="C23" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="E23" s="33">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A24" s="30" t="s">
         <v>224</v>
       </c>
-      <c r="B12" s="48" t="s">
+      <c r="B24" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="C12" s="43" t="s">
-        <v>221</v>
-      </c>
-      <c r="D12" s="42" t="s">
-        <v>265</v>
-      </c>
-      <c r="E12" s="42">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="165" x14ac:dyDescent="0.25">
-      <c r="A13" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="B13" s="45" t="s">
+      <c r="C24" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="E24" s="30">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A25" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="B25" s="33" t="s">
         <v>227</v>
       </c>
-      <c r="D13" s="55" t="s">
-        <v>266</v>
-      </c>
-      <c r="E13" s="45">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="210" x14ac:dyDescent="0.25">
-      <c r="A14" s="49" t="s">
+      <c r="C25" s="33" t="s">
         <v>228</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="D25" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="E25" s="33">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A26" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="B26" s="30" t="s">
         <v>229</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C26" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="D14" s="42" t="s">
-        <v>267</v>
-      </c>
-      <c r="E14" s="42">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="195" x14ac:dyDescent="0.25">
-      <c r="A15" s="45" t="s">
+      <c r="D26" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="E26" s="30">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A27" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="B27" s="33" t="s">
         <v>231</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="C27" s="34" t="s">
         <v>232</v>
       </c>
-      <c r="C15" s="46" t="s">
-        <v>233</v>
-      </c>
-      <c r="D15" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="E15" s="45">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="180" x14ac:dyDescent="0.25">
-      <c r="A16" s="50" t="s">
-        <v>234</v>
-      </c>
-      <c r="B16" s="51" t="s">
-        <v>235</v>
-      </c>
-      <c r="C16" s="52" t="s">
-        <v>236</v>
-      </c>
-      <c r="D16" s="51" t="s">
-        <v>269</v>
-      </c>
-      <c r="E16" s="51">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="135" x14ac:dyDescent="0.25">
-      <c r="A17" s="50" t="s">
-        <v>237</v>
-      </c>
-      <c r="B17" s="51" t="s">
-        <v>238</v>
-      </c>
-      <c r="C17" s="52" t="s">
-        <v>236</v>
-      </c>
-      <c r="D17" s="51" t="s">
-        <v>269</v>
-      </c>
-      <c r="E17" s="51">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A18" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="B18" s="42" t="s">
-        <v>240</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="D18" s="42" t="s">
-        <v>270</v>
-      </c>
-      <c r="E18" s="42">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A19" s="53" t="s">
-        <v>242</v>
-      </c>
-      <c r="B19" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="C19" s="45" t="s">
+      <c r="D27" s="33" t="s">
         <v>244</v>
       </c>
-      <c r="D19" s="45" t="s">
-        <v>267</v>
-      </c>
-      <c r="E19" s="45">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="150" x14ac:dyDescent="0.25">
-      <c r="A20" s="54" t="s">
-        <v>245</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>246</v>
-      </c>
-      <c r="C20" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="D20" s="42" t="s">
-        <v>271</v>
-      </c>
-      <c r="E20" s="42">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="195" x14ac:dyDescent="0.25">
-      <c r="A21" s="44" t="s">
-        <v>248</v>
-      </c>
-      <c r="B21" s="45" t="s">
-        <v>249</v>
-      </c>
-      <c r="C21" s="46" t="s">
-        <v>250</v>
-      </c>
-      <c r="D21" s="45" t="s">
-        <v>272</v>
-      </c>
-      <c r="E21" s="45">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="150" x14ac:dyDescent="0.25">
-      <c r="A22" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="B22" s="42" t="s">
-        <v>252</v>
-      </c>
-      <c r="C22" s="43" t="s">
-        <v>250</v>
-      </c>
-      <c r="D22" s="42" t="s">
-        <v>272</v>
-      </c>
-      <c r="E22" s="42">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="195" x14ac:dyDescent="0.25">
-      <c r="A23" s="45" t="s">
-        <v>253</v>
-      </c>
-      <c r="B23" s="45" t="s">
-        <v>254</v>
-      </c>
-      <c r="C23" s="46" t="s">
-        <v>250</v>
-      </c>
-      <c r="D23" s="45" t="s">
-        <v>272</v>
-      </c>
-      <c r="E23" s="45">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="210" x14ac:dyDescent="0.25">
-      <c r="A24" s="42" t="s">
-        <v>255</v>
-      </c>
-      <c r="B24" s="42" t="s">
-        <v>256</v>
-      </c>
-      <c r="C24" s="43" t="s">
-        <v>250</v>
-      </c>
-      <c r="D24" s="42" t="s">
-        <v>272</v>
-      </c>
-      <c r="E24" s="42">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="195" x14ac:dyDescent="0.25">
-      <c r="A25" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="B25" s="45" t="s">
-        <v>258</v>
-      </c>
-      <c r="C25" s="45" t="s">
-        <v>259</v>
-      </c>
-      <c r="D25" s="45" t="s">
-        <v>273</v>
-      </c>
-      <c r="E25" s="45">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="135" x14ac:dyDescent="0.25">
-      <c r="A26" s="49" t="s">
-        <v>257</v>
-      </c>
-      <c r="B26" s="42" t="s">
-        <v>260</v>
-      </c>
-      <c r="C26" s="43" t="s">
-        <v>261</v>
-      </c>
-      <c r="D26" s="42" t="s">
-        <v>274</v>
-      </c>
-      <c r="E26" s="42">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="165" x14ac:dyDescent="0.25">
-      <c r="A27" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="B27" s="45" t="s">
-        <v>262</v>
-      </c>
-      <c r="C27" s="46" t="s">
-        <v>263</v>
-      </c>
-      <c r="D27" s="45" t="s">
-        <v>275</v>
-      </c>
-      <c r="E27" s="45">
+      <c r="E27" s="33">
         <v>2006</v>
       </c>
     </row>
@@ -4310,22 +3891,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -4348,22 +3929,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -4385,19 +3966,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -4418,16 +3999,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>24</v>
